--- a/Data_Workflow_3_Final_Polishing/Data_dictionaries/lab_dictionary_ms.xlsx
+++ b/Data_Workflow_3_Final_Polishing/Data_dictionaries/lab_dictionary_ms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henryfrye/Dropbox/Intellectual_Endeavours/DimensionsDataPaper/GCFR_Traits/Data_Workflow_3_Final_Polishing/Data_dictionaries/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE0DFFC-A959-2349-A24B-B89E1C35CAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0667ECA-78C3-F443-B303-52D3320F86AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7840" yWindow="1020" windowWidth="27240" windowHeight="15520" xr2:uid="{3AD54CF0-D764-104E-AA26-00318F0EB313}"/>
+    <workbookView xWindow="1560" yWindow="1020" windowWidth="27240" windowHeight="15520" xr2:uid="{3AD54CF0-D764-104E-AA26-00318F0EB313}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,9 +236,6 @@
     <t>A unique value that identifies the collection of a particular species, at a particular location, on a particular day.  The value is based on Date_Sample_Subregion</t>
   </si>
   <si>
-    <t>Latin binomial assigned to plant</t>
-  </si>
-  <si>
     <t>Genus of plant based on the Manning and Goldblatt (2012) taxonomy</t>
   </si>
   <si>
@@ -373,6 +370,9 @@
   </si>
   <si>
     <t>cm/cm</t>
+  </si>
+  <si>
+    <t>Latin binomial assigned to plant based on most recent taxonomy at the time of data collection</t>
   </si>
 </sst>
 </file>
@@ -432,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -446,7 +446,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -834,12 +833,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -859,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -879,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -899,7 +898,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -919,7 +918,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -939,7 +938,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -959,7 +958,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -969,7 +968,7 @@
         <v>-3.1247899999999973</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -980,7 +979,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -989,7 +988,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1000,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -1020,7 +1019,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -1029,7 +1028,7 @@
         <v>45663</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12">
         <v>27</v>
@@ -1040,7 +1039,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
@@ -1060,7 +1059,7 @@
         <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -1080,12 +1079,12 @@
         <v>28</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15">
         <v>34335</v>
       </c>
       <c r="E15" t="s">
@@ -1100,13 +1099,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
@@ -1120,7 +1119,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -1129,7 +1128,7 @@
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17">
         <v>33</v>
@@ -1140,7 +1139,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1149,7 +1148,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18">
         <v>30</v>
@@ -1160,7 +1159,7 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -1169,7 +1168,7 @@
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19">
         <v>40</v>
@@ -1180,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -1189,7 +1188,7 @@
         <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20">
         <v>33</v>
@@ -1200,7 +1199,7 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1209,7 +1208,7 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21">
         <v>43</v>
@@ -1220,7 +1219,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -1229,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22">
         <v>420</v>
@@ -1240,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -1249,7 +1248,7 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23">
         <v>302</v>
@@ -1260,7 +1259,7 @@
         <v>45</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1269,7 +1268,7 @@
         <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24">
         <v>2289</v>
@@ -1280,7 +1279,7 @@
         <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1289,7 +1288,7 @@
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25">
         <v>2374</v>
@@ -1300,7 +1299,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -1309,7 +1308,7 @@
         <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26">
         <v>303</v>
@@ -1320,7 +1319,7 @@
         <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -1329,7 +1328,7 @@
         <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F27">
         <v>529</v>
@@ -1339,8 +1338,8 @@
       <c r="A28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>100</v>
+      <c r="B28" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -1349,7 +1348,7 @@
         <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28">
         <v>508</v>
@@ -1359,8 +1358,8 @@
       <c r="A29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>101</v>
+      <c r="B29" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -1369,7 +1368,7 @@
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F29">
         <v>507</v>
@@ -1379,8 +1378,8 @@
       <c r="A30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>102</v>
+      <c r="B30" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -1389,7 +1388,7 @@
         <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30">
         <v>40</v>
@@ -1399,8 +1398,8 @@
       <c r="A31" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>103</v>
+      <c r="B31" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -1409,7 +1408,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31">
         <v>2407</v>

--- a/Data_Workflow_3_Final_Polishing/Data_dictionaries/lab_dictionary_ms.xlsx
+++ b/Data_Workflow_3_Final_Polishing/Data_dictionaries/lab_dictionary_ms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henryfrye/Dropbox/Intellectual_Endeavours/DimensionsDataPaper/GCFR_Traits/Data_Workflow_3_Final_Polishing/Data_dictionaries/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0667ECA-78C3-F443-B303-52D3320F86AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52AD9CC-8E8C-D44B-876D-43E42B4B334B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1020" windowWidth="27240" windowHeight="15520" xr2:uid="{3AD54CF0-D764-104E-AA26-00318F0EB313}"/>
   </bookViews>
@@ -191,9 +191,6 @@
     <t>0.001346154 - 0.465408805</t>
   </si>
   <si>
-    <t>fwc</t>
-  </si>
-  <si>
     <t>0.11234347 - 84.91666667</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
     </r>
   </si>
   <si>
-    <t>Fresh water content - calculated as (leaf wet mass - leaf dry mass) / leaf dry mass</t>
-  </si>
-  <si>
     <t>g/g</t>
   </si>
   <si>
@@ -373,6 +367,12 @@
   </si>
   <si>
     <t>Latin binomial assigned to plant based on most recent taxonomy at the time of data collection</t>
+  </si>
+  <si>
+    <t>lwc</t>
+  </si>
+  <si>
+    <t>Leaf water content - calculated as (leaf wet mass - leaf dry mass) / leaf dry mass</t>
   </si>
 </sst>
 </file>
@@ -795,22 +795,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
         <v>62</v>
-      </c>
-      <c r="D1" t="s">
-        <v>63</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="102" x14ac:dyDescent="0.2">
@@ -818,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -838,7 +838,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -858,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -878,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -898,7 +898,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -918,7 +918,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -938,7 +938,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -958,7 +958,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -968,7 +968,7 @@
         <v>-3.1247899999999973</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -988,7 +988,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -1019,7 +1019,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -1028,7 +1028,7 @@
         <v>45663</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12">
         <v>27</v>
@@ -1039,7 +1039,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
@@ -1059,7 +1059,7 @@
         <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -1079,7 +1079,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
@@ -1099,13 +1099,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
@@ -1119,7 +1119,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -1128,7 +1128,7 @@
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17">
         <v>33</v>
@@ -1139,7 +1139,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1148,7 +1148,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>30</v>
@@ -1159,7 +1159,7 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -1168,7 +1168,7 @@
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19">
         <v>40</v>
@@ -1179,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -1188,7 +1188,7 @@
         <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>33</v>
@@ -1199,7 +1199,7 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1208,7 +1208,7 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>43</v>
@@ -1219,7 +1219,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22">
         <v>420</v>
@@ -1239,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -1248,7 +1248,7 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23">
         <v>302</v>
@@ -1259,7 +1259,7 @@
         <v>45</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1268,7 +1268,7 @@
         <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24">
         <v>2289</v>
@@ -1279,7 +1279,7 @@
         <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1288,7 +1288,7 @@
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F25">
         <v>2374</v>
@@ -1299,7 +1299,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -1308,7 +1308,7 @@
         <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F26">
         <v>303</v>
@@ -1316,19 +1316,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F27">
         <v>529</v>
@@ -1336,19 +1336,19 @@
     </row>
     <row r="28" spans="1:6" ht="19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
-        <v>54</v>
-      </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28">
         <v>508</v>
@@ -1356,19 +1356,19 @@
     </row>
     <row r="29" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F29">
         <v>507</v>
@@ -1376,19 +1376,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="E30" t="s">
         <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" t="s">
-        <v>103</v>
       </c>
       <c r="F30">
         <v>40</v>
@@ -1396,19 +1396,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>60</v>
-      </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F31">
         <v>2407</v>
